--- a/tests/fixtures/expected/信托计划持仓_完整_管理人.xlsx
+++ b/tests/fixtures/expected/信托计划持仓_完整_管理人.xlsx
@@ -885,7 +885,11 @@
           <t>公募</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>安信基金管理有限责任公司</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -978,7 +982,11 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>华泰柏瑞基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1071,7 +1079,11 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>南方基金管理股份有限公司</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1443,7 +1455,11 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>天弘基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1722,7 +1738,11 @@
           <t>公募</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>汇添富基金管理股份有限公司</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1815,7 +1835,11 @@
           <t>公募</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>华泰柏瑞基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1908,7 +1932,11 @@
           <t>公募</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>国金基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -2280,7 +2308,11 @@
           <t>公募</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>易方达基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>公募基金</t>

--- a/tests/fixtures/expected/信托计划持仓_完整_管理人.xlsx
+++ b/tests/fixtures/expected/信托计划持仓_完整_管理人.xlsx
@@ -696,10 +696,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>景顺长城基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -789,10 +793,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>汇丰晋信基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -979,7 +987,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1076,7 +1084,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1173,10 +1181,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>中欧基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1266,10 +1278,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>华泰保兴基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1359,10 +1375,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>景顺长城基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1452,7 +1472,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>其他</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1549,10 +1569,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>万家基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -1642,10 +1666,14 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>中泰证券(上海)资产管理有限公司</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -2026,10 +2054,14 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>东方基金管理股份有限公司</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -2119,10 +2151,14 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>交银施罗德基金管理有限公司</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>公募基金</t>
@@ -2212,10 +2248,14 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>其他</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>中邮创业基金管理股份有限公司</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>公募基金</t>
